--- a/artfynd/A 36995-2025 artfynd.xlsx
+++ b/artfynd/A 36995-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89601256</v>
+        <v>89601239</v>
       </c>
       <c r="B2" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468816.9022181678</v>
+        <v>468799</v>
       </c>
       <c r="R2" t="n">
-        <v>7094780.919243309</v>
+        <v>7094786</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-09-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89601264</v>
+        <v>89601256</v>
       </c>
       <c r="B3" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468878.9429568084</v>
+        <v>468817</v>
       </c>
       <c r="R3" t="n">
-        <v>7094608.136838607</v>
+        <v>7094781</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2020-09-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-09-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89601261</v>
+        <v>89601245</v>
       </c>
       <c r="B4" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>2079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468845.9180342396</v>
+        <v>468817</v>
       </c>
       <c r="R4" t="n">
-        <v>7094647.994406298</v>
+        <v>7094678</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2020-09-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-09-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89601245</v>
+        <v>89601261</v>
       </c>
       <c r="B5" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468817.1946117085</v>
+        <v>468846</v>
       </c>
       <c r="R5" t="n">
-        <v>7094678.146598723</v>
+        <v>7094648</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,19 +1046,9 @@
           <t>2020-09-28</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-09-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89601257</v>
+        <v>89601264</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468834.9819395283</v>
+        <v>468879</v>
       </c>
       <c r="R6" t="n">
-        <v>7094653.813162892</v>
+        <v>7094608</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,19 +1147,9 @@
           <t>2020-09-28</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-09-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89601239</v>
+        <v>89601257</v>
       </c>
       <c r="B7" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468798.9225909789</v>
+        <v>468835</v>
       </c>
       <c r="R7" t="n">
-        <v>7094785.929919782</v>
+        <v>7094654</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,19 +1248,9 @@
           <t>2020-09-28</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-09-28</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,12 +1284,7 @@
         <v>89601254</v>
       </c>
       <c r="B8" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468877.2015550662</v>
+        <v>468877</v>
       </c>
       <c r="R8" t="n">
-        <v>7094609.911017615</v>
+        <v>7094610</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,19 +1349,9 @@
           <t>2020-09-28</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-09-28</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
